--- a/financials/TCB/TCB.xlsx
+++ b/financials/TCB/TCB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="5520" windowWidth="12000" windowHeight="7380" tabRatio="600" firstSheet="3" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="4545" windowWidth="24000" windowHeight="8355" tabRatio="600" firstSheet="3" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,10 +13,6 @@
     <sheet name="Dự báo tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Hiệu quả thực hiện kế hoạch" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -381,66 +377,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2">
-            <v>26650</v>
-          </cell>
-          <cell r="C2">
-            <v>31650</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="CĐKT"/>
-      <sheetName val="KQHĐKD"/>
-      <sheetName val="LCTT"/>
-      <sheetName val="Phân tích"/>
-      <sheetName val="Dự báo tăng trưởng"/>
-      <sheetName val="Hiệu quả thực hiện KH"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="18">
-          <cell r="F18">
-            <v>25568</v>
-          </cell>
-          <cell r="G18">
-            <v>22888</v>
-          </cell>
-          <cell r="H18">
-            <v>27538</v>
-          </cell>
-          <cell r="I18">
-            <v>32538</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6006,7 +5942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="60.875" bestFit="1" customWidth="1" style="11" min="1" max="1"/>
@@ -8127,6 +8063,45 @@
       </c>
       <c r="J60" s="27" t="n">
         <v>28000000000000</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" s="39">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Tổng lợi nhuận/lỗ trước thuế</t>
+        </is>
+      </c>
+      <c r="B61" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(B$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(C$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(D$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E61" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(E$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F61" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(F$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(G$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(H$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I61" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(I$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -8212,21 +8187,17 @@
           <t>Thị giá</t>
         </is>
       </c>
-      <c r="B3" s="12">
-        <f>[1]Sheet1!C2</f>
-        <v/>
-      </c>
-      <c r="C3" s="12">
-        <f>[1]Sheet1!C2</f>
-        <v/>
-      </c>
-      <c r="D3" s="12">
-        <f>[1]Sheet1!C2</f>
-        <v/>
-      </c>
-      <c r="E3" s="12">
-        <f>[1]Sheet1!C2</f>
-        <v/>
+      <c r="B3" s="12" t="n">
+        <v>31650</v>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>31650</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>31650</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>31650</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -9535,19 +9506,19 @@
         </is>
       </c>
       <c r="B3" s="43">
-        <f>[2]KQHĐKD!F18*1000</f>
+        <f>chi_so_tai_chinh!F61/1000000</f>
         <v/>
       </c>
       <c r="C3" s="43">
-        <f>[2]KQHĐKD!G18*1000</f>
+        <f>chi_so_tai_chinh!G61/1000000</f>
         <v/>
       </c>
       <c r="D3" s="43">
-        <f>[2]KQHĐKD!H18*1000</f>
+        <f>chi_so_tai_chinh!H61/1000000</f>
         <v/>
       </c>
       <c r="E3" s="43">
-        <f>[2]KQHĐKD!I18*1000</f>
+        <f>chi_so_tai_chinh!I61/1000000</f>
         <v/>
       </c>
       <c r="F3" s="42" t="n"/>
@@ -37524,13 +37495,13 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:E4">
-    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
+  <conditionalFormatting sqref="B8">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
+  <conditionalFormatting sqref="B4:E4">
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/financials/TCB/TCB.xlsx
+++ b/financials/TCB/TCB.xlsx
@@ -1743,16 +1743,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>7583090000000</v>
+        <v>7572229000000</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>10052963000000</v>
+        <v>10041556000000</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>8357447000000</v>
+        <v>8347576000000</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5074479000000</v>
+        <v>5070812000000</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>961034000000</v>
@@ -1773,10 +1773,18 @@
           <t>Chứng khoán kinh doanh</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr"/>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
+      <c r="B36" s="4" t="n">
+        <v>7583090000000</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>10052963000000</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>8357447000000</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>5074479000000</v>
+      </c>
       <c r="F36" s="4" t="n">
         <v>961034000000</v>
       </c>
@@ -1859,16 +1867,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>159939217000000</v>
+        <v>157554103000000</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>230802027000000</v>
+        <v>227885283000000</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>277524615000000</v>
+        <v>275310367000000</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>347341244000000</v>
+        <v>343605581000000</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>420523705000000</v>
@@ -1889,10 +1897,18 @@
           <t>Cho vay khách hàng</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr"/>
-      <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
+      <c r="B40" s="4" t="n">
+        <v>159939217000000</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>230802027000000</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>277524615000000</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>347341244000000</v>
+      </c>
       <c r="F40" s="4" t="n">
         <v>420523705000000</v>
       </c>
@@ -2068,16 +2084,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>717481000000</v>
+        <v>17701805000000</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1055475000000</v>
+        <v>19334394000000</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1268562000000</v>
+        <v>22835903000000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1448617000000</v>
+        <v>34710635000000</v>
       </c>
       <c r="F46" s="4" t="n">
         <v>1616735000000</v>
@@ -3028,10 +3044,18 @@
           <t>Tài sản Có khác</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr"/>
-      <c r="C77" s="4" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="B77" s="4" t="n">
+        <v>717481000000</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>1055475000000</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>1268562000000</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>1448617000000</v>
+      </c>
       <c r="F77" s="4" t="n">
         <v>1616735000000</v>
       </c>
